--- a/codigos/Codigos_resNet/datos/deuda multilaterales.xlsx
+++ b/codigos/Codigos_resNet/datos/deuda multilaterales.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\Codigos_resNet\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\codigos\Codigos_resNet\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581B2037-F882-437D-9434-BBB603CED65F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C854EA-76F8-4151-AEC0-EEA807F31116}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="3390" windowWidth="14490" windowHeight="7875" activeTab="3" xr2:uid="{CAA6EF67-7BC3-4A65-9827-9E2B82094EBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{CAA6EF67-7BC3-4A65-9827-9E2B82094EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="deuMult" sheetId="1" r:id="rId1"/>
     <sheet name="bopreal_1" sheetId="3" r:id="rId2"/>
     <sheet name="bopreal_2" sheetId="4" r:id="rId3"/>
     <sheet name="bopreal_3" sheetId="5" r:id="rId4"/>
-    <sheet name="bopreal_4" sheetId="6" r:id="rId5"/>
-    <sheet name="dep y encajes" sheetId="2" r:id="rId6"/>
+    <sheet name="Hoja1" sheetId="7" r:id="rId5"/>
+    <sheet name="bopreal_4" sheetId="6" r:id="rId6"/>
+    <sheet name="dep y encajes" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>fecha</t>
   </si>
@@ -58,12 +59,18 @@
   <si>
     <t>FFj</t>
   </si>
+  <si>
+    <t>otros pasivos_pesos</t>
+  </si>
+  <si>
+    <t>otros pasivos_usd</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="22">
+  <numFmts count="21">
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
@@ -85,9 +92,8 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00\ [$€]_-;\-* #,##0.00\ [$€]_-;_-* &quot;-&quot;??\ [$€]_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
-    <numFmt numFmtId="181" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +327,12 @@
     <font>
       <sz val="10"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="28">
@@ -614,7 +626,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="693">
+  <cellStyleXfs count="694">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1333,18 +1345,20 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="693">
+  <cellStyles count="694">
     <cellStyle name="20% - Accent1" xfId="4" xr:uid="{DFDBF0D3-4484-4FCA-A994-E23AD0A68789}"/>
     <cellStyle name="20% - Accent2" xfId="5" xr:uid="{BDA045F4-FA20-4C4B-AE88-9B6028909DAC}"/>
     <cellStyle name="20% - Accent3" xfId="6" xr:uid="{F59C922F-E438-46CC-8F3D-D3A51F797E9A}"/>
@@ -1852,6 +1866,7 @@
     <cellStyle name="Normal 14" xfId="3" xr:uid="{3DA346A9-512C-46A8-BD2D-B3A9D8357817}"/>
     <cellStyle name="Normal 14 2" xfId="603" xr:uid="{5817A0F9-75FC-4D3B-A3B9-F575F93FABC3}"/>
     <cellStyle name="Normal 15" xfId="609" xr:uid="{2B243177-1FD6-4BEA-8FE9-BCCE1950F431}"/>
+    <cellStyle name="Normal 16" xfId="693" xr:uid="{5797D2F4-48C7-44B8-87E5-BCE010DE1228}"/>
     <cellStyle name="Normal 2" xfId="367" xr:uid="{6357C82D-B62E-4901-96BD-1BC1A87D7E95}"/>
     <cellStyle name="Normal 2 2" xfId="412" xr:uid="{DF8D4D17-FFAC-448A-BB73-00FC5A7504CB}"/>
     <cellStyle name="Normal 2 2 2" xfId="449" xr:uid="{46E544CE-DBC0-4AE1-AD15-12342BBA24EC}"/>
@@ -2372,7 +2387,7 @@
       <c r="A2" s="1">
         <v>43831</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>150366.36496000001</v>
       </c>
     </row>
@@ -3027,7 +3042,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -3035,7 +3050,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>45296</v>
       </c>
       <c r="B2">
@@ -3043,7 +3058,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>45566</v>
       </c>
       <c r="B3">
@@ -3051,7 +3066,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <f>+A3+180</f>
         <v>45746</v>
       </c>
@@ -3060,7 +3075,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <f t="shared" ref="A5:A8" si="0">+A4+180</f>
         <v>45926</v>
       </c>
@@ -3069,7 +3084,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <f t="shared" si="0"/>
         <v>46106</v>
       </c>
@@ -3078,7 +3093,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>46286</v>
       </c>
@@ -3087,7 +3102,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>46466</v>
       </c>
@@ -3096,7 +3111,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>46478</v>
       </c>
       <c r="B9">
@@ -3104,7 +3119,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <f>+A8+180</f>
         <v>46646</v>
       </c>
@@ -3113,7 +3128,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>46661</v>
       </c>
       <c r="B11">
@@ -3130,11 +3145,11 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
+    <col min="1" max="1" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -3142,7 +3157,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>45338</v>
       </c>
       <c r="B2">
@@ -3150,7 +3165,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>45503</v>
       </c>
       <c r="B3">
@@ -3158,7 +3173,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>45534</v>
       </c>
       <c r="B4">
@@ -3166,7 +3181,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>45565</v>
       </c>
       <c r="B5">
@@ -3174,7 +3189,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>45595</v>
       </c>
       <c r="B6">
@@ -3182,7 +3197,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>45626</v>
       </c>
       <c r="B7">
@@ -3190,7 +3205,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>45656</v>
       </c>
       <c r="B8">
@@ -3198,7 +3213,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>45687</v>
       </c>
       <c r="B9">
@@ -3206,7 +3221,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>45716</v>
       </c>
       <c r="B10">
@@ -3214,7 +3229,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>45746</v>
       </c>
       <c r="B11">
@@ -3222,7 +3237,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>45777</v>
       </c>
       <c r="B12">
@@ -3230,7 +3245,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>45807</v>
       </c>
       <c r="B13">
@@ -3238,7 +3253,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>45838</v>
       </c>
       <c r="B14">
@@ -3255,11 +3270,11 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
+    <col min="1" max="1" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -3267,7 +3282,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>45296</v>
       </c>
       <c r="B2">
@@ -3275,7 +3290,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>45534</v>
       </c>
       <c r="B3">
@@ -3283,7 +3298,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>45626</v>
       </c>
       <c r="B4">
@@ -3291,7 +3306,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>45716</v>
       </c>
       <c r="B5">
@@ -3299,7 +3314,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>45807</v>
       </c>
       <c r="B6">
@@ -3307,7 +3322,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>45899</v>
       </c>
       <c r="B7">
@@ -3315,7 +3330,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>45991</v>
       </c>
       <c r="B8">
@@ -3323,7 +3338,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>46081</v>
       </c>
       <c r="B9">
@@ -3331,7 +3346,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>46173</v>
       </c>
       <c r="B10">
@@ -3344,83 +3359,376 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D6D83E-DB14-4B92-98F5-FBCBC28443B2}">
-  <dimension ref="A1:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B4C800-A606-4B5A-9D13-301E65E92F23}">
+  <dimension ref="B2:B74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="7"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="7">
-        <v>45832</v>
-      </c>
-      <c r="B2">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="7">
-        <v>45961</v>
-      </c>
-      <c r="B3">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="7">
-        <v>46142</v>
-      </c>
-      <c r="B4">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="7">
-        <v>46326</v>
-      </c>
-      <c r="B5">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="7">
-        <v>46507</v>
-      </c>
-      <c r="B6">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="7">
-        <v>46691</v>
-      </c>
-      <c r="B7">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="7">
-        <v>46873</v>
-      </c>
-      <c r="B8">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="7">
-        <v>47057</v>
-      </c>
-      <c r="B9">
-        <v>913.5</v>
+    <row r="2" spans="2:2">
+      <c r="B2" s="7">
+        <v>-1370126479</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="7">
+        <v>-1398669254</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="7">
+        <v>-1398672138</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="7">
+        <v>-1456348285</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="7">
+        <v>-1480395610</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="7">
+        <v>-1570166301</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="7">
+        <v>-1630595666</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="7">
+        <v>-1698040394</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="7">
+        <v>-1755571380</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="7">
+        <v>-1827682802</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="7">
+        <v>-1924834725</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="7">
+        <v>-2005793007</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="7">
+        <v>-2107814326</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="7">
+        <v>-2155790324</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="7">
+        <v>-2184083594</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="7">
+        <v>-2244730982</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="7">
+        <v>-2303428723</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="7">
+        <v>-2304840509</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="7">
+        <v>-2323205080</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="7">
+        <v>-2348721188</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="7">
+        <v>-2376401423</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="7">
+        <v>-2412832643</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="7">
+        <v>-2454292859</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="7">
+        <v>-2501811794</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="7">
+        <v>-2594244558</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="7">
+        <v>-2668953662</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="7">
+        <v>-2747515678</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="7">
+        <v>-2755125787</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="7">
+        <v>-2844009869</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="7">
+        <v>-2951536249</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="7">
+        <v>-3075803621</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="7">
+        <v>-3191142284</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="7">
+        <v>-3299789538</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="7">
+        <v>-3442662236</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="7">
+        <v>-3760365387</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="7">
+        <v>-4081800986</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="7">
+        <v>-4385938691</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="7">
+        <v>-4519830301</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="7">
+        <v>-4837637964</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="7">
+        <v>-5136193016</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="7">
+        <v>-5390670085</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="7">
+        <v>-5698423171</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="7">
+        <v>-6454178750</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="7">
+        <v>-7743279051</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="7">
+        <v>-7720718742</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="7">
+        <v>-7716849790</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="7">
+        <v>-8075104898</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="7">
+        <v>-17625718258</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="7">
+        <v>-17769502740</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="7">
+        <v>-17496481022</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="7">
+        <v>-16951485555</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="7">
+        <v>-16986341389</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="7">
+        <v>-17326595692</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="7">
+        <v>-17484978386</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="7">
+        <v>-17937111126</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="7">
+        <v>-18621380627</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="7">
+        <v>-19204084771</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="7">
+        <v>-19347818824</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="7">
+        <v>-19380981932</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="7">
+        <v>-19617869753</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="7">
+        <v>-21216656323</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="7">
+        <v>-21334490010</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="7">
+        <v>-21627605139</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="7">
+        <v>-23601983312</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="7">
+        <v>-24263323980</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="7">
+        <v>-26767080944</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="7">
+        <v>-30118504542</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="7">
+        <v>-29738133453</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="7">
+        <v>-30797118125</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="7">
+        <v>-32468820360</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="7">
+        <v>-32797173611</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="7">
+        <v>-37044056094</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="7">
+        <v>-41152534525</v>
       </c>
     </row>
   </sheetData>
@@ -3429,15 +3737,105 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66326B90-32E5-4EC9-AB59-9078B62DF326}">
-  <dimension ref="A1:F74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D6D83E-DB14-4B92-98F5-FBCBC28443B2}">
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:2">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="6">
+        <v>45832</v>
+      </c>
+      <c r="B2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="6">
+        <v>45961</v>
+      </c>
+      <c r="B3">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B4">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="6">
+        <v>46326</v>
+      </c>
+      <c r="B5">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="6">
+        <v>46507</v>
+      </c>
+      <c r="B6">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="6">
+        <v>46691</v>
+      </c>
+      <c r="B7">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6">
+        <v>46873</v>
+      </c>
+      <c r="B8">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="6">
+        <v>47057</v>
+      </c>
+      <c r="B9">
+        <v>913.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66326B90-32E5-4EC9-AB59-9078B62DF326}">
+  <dimension ref="A1:H74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3447,7 +3845,7 @@
       <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E1" t="s">
@@ -3456,18 +3854,24 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>43831</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>4621146.1624400001</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>600823521</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>60.331200000000003</v>
       </c>
       <c r="E2">
@@ -3478,18 +3882,25 @@
         <f>+C2/D2</f>
         <v>9958753.0332564246</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="8">
+        <v>-1370126479</v>
+      </c>
+      <c r="H2" s="2">
+        <f>+-G2/(D2*1000)</f>
+        <v>22710.081665871057</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>43862</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>3854504.9322700002</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>661055139</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>62.207999999999998</v>
       </c>
       <c r="E3">
@@ -3500,18 +3911,25 @@
         <f t="shared" ref="F3:F66" si="1">+C3/D3</f>
         <v>10626529.369212963</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="8">
+        <v>-1398669254</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H66" si="2">+-G3/(D3*1000)</f>
+        <v>22483.752154063786</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>43891</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>5957522.4149499405</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>664987919</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>64.469700000000003</v>
       </c>
       <c r="E4">
@@ -3522,18 +3940,25 @@
         <f t="shared" si="1"/>
         <v>10314735.744078225</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="8">
+        <v>-1398672138</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
+        <v>21695.030968036146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>43922</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>7874261.0983799994</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>726395568</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>66.834999999999994</v>
       </c>
       <c r="E5">
@@ -3544,18 +3969,25 @@
         <f t="shared" si="1"/>
         <v>10868490.581282264</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="8">
+        <v>-1456348285</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>21790.204009875066</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>43952</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>4663849.4802100006</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>769004804</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>68.534999999999997</v>
       </c>
       <c r="E6">
@@ -3566,18 +3998,25 @@
         <f t="shared" si="1"/>
         <v>11220614.343036406</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="8">
+        <v>-1480395610</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>21600.577952870797</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>43983</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>6895817.6874099998</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>740880957</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>70.454999999999998</v>
       </c>
       <c r="E7">
@@ -3588,18 +4027,25 @@
         <f t="shared" si="1"/>
         <v>10515661.869278263</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="8">
+        <v>-1570166301</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>22286.087587822014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>44013</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>4714200</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>774669062</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>72.314999999999998</v>
       </c>
       <c r="E8">
@@ -3610,18 +4056,25 @@
         <f t="shared" si="1"/>
         <v>10712425.665491253</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="8">
+        <v>-1630595666</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>22548.512286524234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>44044</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>6562570.2446300015</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>845913711</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>74.174999999999997</v>
       </c>
       <c r="E9">
@@ -3632,18 +4085,25 @@
         <f t="shared" si="1"/>
         <v>11404296.744186047</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="8">
+        <v>-1698040394</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>22892.354486012806</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>44075</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>7312037.9125500005</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>913735293</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>76.174999999999997</v>
       </c>
       <c r="E10">
@@ -3654,18 +4114,25 @@
         <f t="shared" si="1"/>
         <v>11995212.248112898</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="8">
+        <v>-1755571380</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>23046.555694125371</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>44105</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>6539575.0217900006</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>901008055</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>78.328299999999999</v>
       </c>
       <c r="E11">
@@ -3676,18 +4143,25 @@
         <f t="shared" si="1"/>
         <v>11502969.616345562</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="8">
+        <v>-1827682802</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>23333.620185807682</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>44136</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>8523990.1096999999</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>908878211</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>81.296700000000001</v>
       </c>
       <c r="E12">
@@ -3698,18 +4172,25 @@
         <f t="shared" si="1"/>
         <v>11179767.57974186</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="8">
+        <v>-1924834725</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="2"/>
+        <v>23676.664919978302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>44166</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>43425726.832810007</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>918560327</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>84.144999999999996</v>
       </c>
       <c r="E13">
@@ -3720,18 +4201,25 @@
         <f t="shared" si="1"/>
         <v>10916398.205478638</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="8">
+        <v>-2005793007</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="2"/>
+        <v>23837.340388614892</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>44197</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>9642581.6524000019</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>999238358</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>87.298299999999998</v>
       </c>
       <c r="E14">
@@ -3742,18 +4230,25 @@
         <f t="shared" si="1"/>
         <v>11446252.195059927</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="8">
+        <v>-2107814326</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="2"/>
+        <v>24144.9641745601</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>44228</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>6463230.848979516</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>1064065221</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>89.825000000000003</v>
       </c>
       <c r="E15">
@@ -3764,18 +4259,25 @@
         <f t="shared" si="1"/>
         <v>11845980.751461174</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="8">
+        <v>-2155790324</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="2"/>
+        <v>23999.892279432228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>44256</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>13425788.8233</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>1031992846</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>91.984999999999999</v>
       </c>
       <c r="E16">
@@ -3786,18 +4288,25 @@
         <f t="shared" si="1"/>
         <v>11219142.751535576</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="8">
+        <v>-2184083594</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="2"/>
+        <v>23743.910354949177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>44287</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>6042516.8568500001</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>985805325</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>93.555000000000007</v>
       </c>
       <c r="E17">
@@ -3808,18 +4317,25 @@
         <f t="shared" si="1"/>
         <v>10537174.122174121</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="8">
+        <v>-2244730982</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="2"/>
+        <v>23993.704045748491</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>44317</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>6732039.4484399995</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="3">
         <v>956610531</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>94.685000000000002</v>
       </c>
       <c r="E18">
@@ -3830,18 +4346,25 @@
         <f t="shared" si="1"/>
         <v>10103084.237207582</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="8">
+        <v>-2303428723</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="2"/>
+        <v>24327.282283360615</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>44348</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>6261742.7438300001</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="3">
         <v>1023338374</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>95.726699999999994</v>
       </c>
       <c r="E19">
@@ -3852,18 +4375,25 @@
         <f t="shared" si="1"/>
         <v>10690208.416251684</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="8">
+        <v>-2304840509</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="2"/>
+        <v>24077.300366564396</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>44378</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>29308181.6642</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <v>1083760015</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>96.685000000000002</v>
       </c>
       <c r="E20">
@@ -3874,18 +4404,25 @@
         <f t="shared" si="1"/>
         <v>11209184.620158246</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="8">
+        <v>-2323205080</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="2"/>
+        <v>24028.598851941872</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>44409</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>23960010.025589999</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>1110841764</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="8">
         <v>97.7517</v>
       </c>
       <c r="E21">
@@ -3896,18 +4433,25 @@
         <f t="shared" si="1"/>
         <v>11363912.484386461</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="8">
+        <v>-2348721188</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="2"/>
+        <v>24027.420372228822</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>44440</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>19415045.118840002</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>1171291595</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="8">
         <v>98.734999999999999</v>
       </c>
       <c r="E22">
@@ -3918,18 +4462,25 @@
         <f t="shared" si="1"/>
         <v>11862982.680913556</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="8">
+        <v>-2376401423</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="2"/>
+        <v>24068.480508431661</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>44470</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>24271465.688919999</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>1187706064</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="8">
         <v>99.721699999999998</v>
       </c>
       <c r="E23">
@@ -3940,18 +4491,25 @@
         <f t="shared" si="1"/>
         <v>11910206.745372372</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="8">
+        <v>-2412832643</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="2"/>
+        <v>24195.662960017729</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>44501</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>102221390.25857002</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>1155245496</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="8">
         <v>100.925</v>
       </c>
       <c r="E24">
@@ -3962,18 +4520,25 @@
         <f t="shared" si="1"/>
         <v>11446574.149120634</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="8">
+        <v>-2454292859</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="2"/>
+        <v>24317.987208323011</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>44531</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>83602762.309670001</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>1244592073</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="8">
         <v>102.75</v>
       </c>
       <c r="E25">
@@ -3984,18 +4549,25 @@
         <f t="shared" si="1"/>
         <v>12112818.228710461</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="8">
+        <v>-2501811794</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" si="2"/>
+        <v>24348.533274939171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>44562</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>101093132.56847002</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>1263626022</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="8">
         <v>105.015</v>
       </c>
       <c r="E26">
@@ -4006,18 +4578,25 @@
         <f t="shared" si="1"/>
         <v>12032814.569347236</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="8">
+        <v>-2594244558</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="2"/>
+        <v>24703.5619482931</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>44593</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="3">
         <v>19082084.820069999</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <v>1309298699</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="8">
         <v>107.4417</v>
       </c>
       <c r="E27">
@@ -4028,18 +4607,25 @@
         <f t="shared" si="1"/>
         <v>12186131.632317806</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="8">
+        <v>-2668953662</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="2"/>
+        <v>24840.947807043263</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>44621</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>767243478.78443003</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <v>1283781847</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="8">
         <v>110.9783</v>
       </c>
       <c r="E28">
@@ -4050,18 +4636,25 @@
         <f t="shared" si="1"/>
         <v>11567863.690469217</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="8">
+        <v>-2747515678</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="2"/>
+        <v>24757.233423110643</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>44652</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="3">
         <v>687400953.66190004</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3">
         <v>1416125131</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="8">
         <v>115.3117</v>
       </c>
       <c r="E29">
@@ -4072,18 +4665,25 @@
         <f t="shared" si="1"/>
         <v>12280845.144074712</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="8">
+        <v>-2755125787</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="2"/>
+        <v>23892.85551249353</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>44682</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="3">
         <v>353501053.55596995</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3">
         <v>1453945935</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="8">
         <v>120.1617</v>
       </c>
       <c r="E30">
@@ -4094,18 +4694,25 @@
         <f t="shared" si="1"/>
         <v>12099911.494261483</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="8">
+        <v>-2844009869</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="2"/>
+        <v>23668.18935650877</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>44713</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="3">
         <v>526400571.37887996</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3">
         <v>1442653786</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="8">
         <v>125.215</v>
       </c>
       <c r="E31">
@@ -4116,18 +4723,25 @@
         <f t="shared" si="1"/>
         <v>11521413.456854211</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="8">
+        <v>-2951536249</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="2"/>
+        <v>23571.746587868867</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>44743</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3">
         <v>293787964.17534</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3">
         <v>1506415296</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="8">
         <v>131.22669999999999</v>
       </c>
       <c r="E32">
@@ -4138,18 +4752,25 @@
         <f t="shared" si="1"/>
         <v>11479487.756683663</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" s="8">
+        <v>-3075803621</v>
+      </c>
+      <c r="H32" s="2">
+        <f t="shared" si="2"/>
+        <v>23438.855210105874</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>44774</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="3">
         <v>282120955.72248995</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>1600898840</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="8">
         <v>138.7133</v>
       </c>
       <c r="E33">
@@ -4160,18 +4781,25 @@
         <f t="shared" si="1"/>
         <v>11541062.320628231</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" s="8">
+        <v>-3191142284</v>
+      </c>
+      <c r="H33" s="2">
+        <f t="shared" si="2"/>
+        <v>23005.308676240849</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>44805</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="3">
         <v>23170811.327040002</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>1626652128</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="8">
         <v>147.315</v>
       </c>
       <c r="E34">
@@ -4182,18 +4810,25 @@
         <f t="shared" si="1"/>
         <v>11041999.307606149</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="8">
+        <v>-3299789538</v>
+      </c>
+      <c r="H34" s="2">
+        <f t="shared" si="2"/>
+        <v>22399.548844313205</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>44835</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="3">
         <v>510972385.00199002</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <v>1760792329</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="8">
         <v>156.89500000000001</v>
       </c>
       <c r="E35">
@@ -4204,18 +4839,25 @@
         <f t="shared" si="1"/>
         <v>11222743.420759106</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="8">
+        <v>-3442662236</v>
+      </c>
+      <c r="H35" s="2">
+        <f t="shared" si="2"/>
+        <v>21942.459836196183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>44866</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="3">
         <v>420310038.30346</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>1927646958</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="8">
         <v>167.255</v>
       </c>
       <c r="E36">
@@ -4226,18 +4868,25 @@
         <f t="shared" si="1"/>
         <v>11525197.799766824</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="8">
+        <v>-3760365387</v>
+      </c>
+      <c r="H36" s="2">
+        <f t="shared" si="2"/>
+        <v>22482.827939374009</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>44896</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="3">
         <v>855046491.41350007</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="3">
         <v>2141070655</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="8">
         <v>177.1283</v>
       </c>
       <c r="E37">
@@ -4248,18 +4897,25 @@
         <f t="shared" si="1"/>
         <v>12087682.516006758</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="8">
+        <v>-4081800986</v>
+      </c>
+      <c r="H37" s="2">
+        <f t="shared" si="2"/>
+        <v>23044.318643604667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>44927</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="3">
         <v>245440395.27162999</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="3">
         <v>2408870795</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="8">
         <v>186.875</v>
       </c>
       <c r="E38">
@@ -4270,18 +4926,25 @@
         <f t="shared" si="1"/>
         <v>12890278.50167224</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38" s="8">
+        <v>-4385938691</v>
+      </c>
+      <c r="H38" s="2">
+        <f t="shared" si="2"/>
+        <v>23469.906038795987</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>44958</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="3">
         <v>78160765.615800008</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="3">
         <v>2554097417</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="8">
         <v>197.1533</v>
       </c>
       <c r="E39">
@@ -4292,18 +4955,25 @@
         <f t="shared" si="1"/>
         <v>12954880.374814928</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="8">
+        <v>-4519830301</v>
+      </c>
+      <c r="H39" s="2">
+        <f t="shared" si="2"/>
+        <v>22925.461054925279</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>44986</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="3">
         <v>711777372.05326998</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="3">
         <v>2536997821</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="8">
         <v>208.98830000000001</v>
       </c>
       <c r="E40">
@@ -4314,18 +4984,25 @@
         <f t="shared" si="1"/>
         <v>12139425.130497735</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="8">
+        <v>-4837637964</v>
+      </c>
+      <c r="H40" s="2">
+        <f t="shared" si="2"/>
+        <v>23147.888967947008</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>45017</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="3">
         <v>93077444.507949993</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="3">
         <v>2501824243</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="8">
         <v>222.57499999999999</v>
       </c>
       <c r="E41">
@@ -4336,18 +5013,25 @@
         <f t="shared" si="1"/>
         <v>11240365.014040211</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="8">
+        <v>-5136193016</v>
+      </c>
+      <c r="H41" s="2">
+        <f t="shared" si="2"/>
+        <v>23076.235048859933</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>45047</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="3">
         <v>20948051.250060003</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="3">
         <v>2636887694</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="8">
         <v>239.32499999999999</v>
       </c>
       <c r="E42">
@@ -4358,18 +5042,25 @@
         <f t="shared" si="1"/>
         <v>11018020.240259062</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" s="8">
+        <v>-5390670085</v>
+      </c>
+      <c r="H42" s="2">
+        <f t="shared" si="2"/>
+        <v>22524.47544134545</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>45078</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="3">
         <v>28919359.163549997</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="3">
         <v>2643892702</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="8">
         <v>256.67500000000001</v>
       </c>
       <c r="E43">
@@ -4380,18 +5071,25 @@
         <f t="shared" si="1"/>
         <v>10300546.223823901</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="8">
+        <v>-5698423171</v>
+      </c>
+      <c r="H43" s="2">
+        <f t="shared" si="2"/>
+        <v>22200.927908834128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>45108</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="3">
         <v>16095561.08114</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="3">
         <v>2706242392</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="8">
         <v>275.2833</v>
       </c>
       <c r="E44">
@@ -4402,18 +5100,25 @@
         <f t="shared" si="1"/>
         <v>9830753.9614644255</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="8">
+        <v>-6454178750</v>
+      </c>
+      <c r="H44" s="2">
+        <f t="shared" si="2"/>
+        <v>23445.587690935121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>45139</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="3">
         <v>1490807517.8262401</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="3">
         <v>3280147380</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="8">
         <v>350.01670000000001</v>
       </c>
       <c r="E45">
@@ -4424,18 +5129,25 @@
         <f t="shared" si="1"/>
         <v>9371402.5073660761</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" s="8">
+        <v>-7743279051</v>
+      </c>
+      <c r="H45" s="2">
+        <f t="shared" si="2"/>
+        <v>22122.59886742547</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>45170</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="3">
         <v>1259523770.4477899</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="3">
         <v>3349149888</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="8">
         <v>350.00830000000002</v>
       </c>
       <c r="E46">
@@ -4446,18 +5158,25 @@
         <f t="shared" si="1"/>
         <v>9568772.7633887529</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="8">
+        <v>-7720718742</v>
+      </c>
+      <c r="H46" s="2">
+        <f t="shared" si="2"/>
+        <v>22058.673300033166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1">
         <v>45200</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="3">
         <v>416720710.45837998</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="3">
         <v>3109212179</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="8">
         <v>350.00830000000002</v>
       </c>
       <c r="E47">
@@ -4468,18 +5187,25 @@
         <f t="shared" si="1"/>
         <v>8883252.7085786238</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" s="8">
+        <v>-7716849790</v>
+      </c>
+      <c r="H47" s="2">
+        <f t="shared" si="2"/>
+        <v>22047.61941359676</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>45231</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="3">
         <v>23123839.360650003</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="3">
         <v>3190928310</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="8">
         <v>360.52499999999998</v>
       </c>
       <c r="E48">
@@ -4490,18 +5216,25 @@
         <f t="shared" si="1"/>
         <v>8850782.3590597045</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="8">
+        <v>-8075104898</v>
+      </c>
+      <c r="H48" s="2">
+        <f t="shared" si="2"/>
+        <v>22398.182922127453</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>45261</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="3">
         <v>50812945.520859994</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="3">
         <v>7371126317</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="8">
         <v>808.48329999999999</v>
       </c>
       <c r="E49">
@@ -4512,18 +5245,25 @@
         <f t="shared" si="1"/>
         <v>9117227.6743378621</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="8">
+        <v>-17625718258</v>
+      </c>
+      <c r="H49" s="2">
+        <f t="shared" si="2"/>
+        <v>21800.967636560956</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>45292</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="3">
         <v>2286627572.97679</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="3">
         <v>8095232818</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="8">
         <v>826.25</v>
       </c>
       <c r="E50">
@@ -4534,18 +5274,25 @@
         <f t="shared" si="1"/>
         <v>9797558.6299546137</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="8">
+        <v>-17769502740</v>
+      </c>
+      <c r="H50" s="2">
+        <f t="shared" si="2"/>
+        <v>21506.206039334342</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>45323</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="3">
         <v>1486519166.0609798</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="3">
         <v>7846451517</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="8">
         <v>842.25</v>
       </c>
       <c r="E51">
@@ -4556,18 +5303,25 @@
         <f t="shared" si="1"/>
         <v>9316059.9786286727</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" s="8">
+        <v>-17496481022</v>
+      </c>
+      <c r="H51" s="2">
+        <f t="shared" si="2"/>
+        <v>20773.500768180467</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>45352</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="3">
         <v>886469720.33432996</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="3">
         <v>7629157640</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="8">
         <v>857.41669999999999</v>
       </c>
       <c r="E52">
@@ -4578,18 +5332,25 @@
         <f t="shared" si="1"/>
         <v>8897841.2013668492</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="8">
+        <v>-16951485555</v>
+      </c>
+      <c r="H52" s="2">
+        <f t="shared" si="2"/>
+        <v>19770.416828830137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>45383</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="3">
         <v>950292291.21390998</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="3">
         <v>7351718245</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="8">
         <v>876.75</v>
       </c>
       <c r="E53">
@@ -4600,18 +5361,25 @@
         <f t="shared" si="1"/>
         <v>8385193.3219275735</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="8">
+        <v>-16986341389</v>
+      </c>
+      <c r="H53" s="2">
+        <f t="shared" si="2"/>
+        <v>19374.21316110636</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>45413</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="3">
         <v>383156210.37596005</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="3">
         <v>7267834206</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="8">
         <v>895.25</v>
       </c>
       <c r="E54">
@@ -4622,18 +5390,25 @@
         <f t="shared" si="1"/>
         <v>8118217.4878525548</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="8">
+        <v>-17326595692</v>
+      </c>
+      <c r="H54" s="2">
+        <f t="shared" si="2"/>
+        <v>19353.918672996369</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>45444</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="3">
         <v>942654423.41727006</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="3">
         <v>7587839026</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="8">
         <v>911.75</v>
       </c>
       <c r="E55">
@@ -4644,18 +5419,25 @@
         <f t="shared" si="1"/>
         <v>8322280.2588428846</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="8">
+        <v>-17484978386</v>
+      </c>
+      <c r="H55" s="2">
+        <f t="shared" si="2"/>
+        <v>19177.382381135179</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>45474</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="3">
         <v>1159247788.9581399</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>8941990710</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="8">
         <v>932.75</v>
       </c>
       <c r="E56">
@@ -4666,18 +5448,25 @@
         <f t="shared" si="1"/>
         <v>9586696.0171535779</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="8">
+        <v>-17937111126</v>
+      </c>
+      <c r="H56" s="2">
+        <f t="shared" si="2"/>
+        <v>19230.352319485391</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>45505</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="3">
         <v>795953757.33887994</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="3">
         <v>9039337888</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="8">
         <v>952.83330000000001</v>
       </c>
       <c r="E57">
@@ -4688,18 +5477,25 @@
         <f t="shared" si="1"/>
         <v>9486798.8849676009</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" s="8">
+        <v>-18621380627</v>
+      </c>
+      <c r="H57" s="2">
+        <f t="shared" si="2"/>
+        <v>19543.167337875366</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>45536</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="3">
         <v>1540884219.8592198</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="3">
         <v>10344453846</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="8">
         <v>970.91669999999999</v>
       </c>
       <c r="E58">
@@ -4710,18 +5506,25 @@
         <f t="shared" si="1"/>
         <v>10654316.52993506</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="8">
+        <v>-19204084771</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="2"/>
+        <v>19779.333047829954</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>45566</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="3">
         <v>1264155313.35919</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="3">
         <v>12450855362</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="8">
         <v>990.75</v>
       </c>
       <c r="E59">
@@ -4732,18 +5535,25 @@
         <f t="shared" si="1"/>
         <v>12567101.046681806</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="8">
+        <v>-19347818824</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="2"/>
+        <v>19528.457051728488</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>45597</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="3">
         <v>3602086501.0905299</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="3">
         <v>13722835963</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="8">
         <v>1011.75</v>
       </c>
       <c r="E60">
@@ -4754,18 +5564,25 @@
         <f t="shared" si="1"/>
         <v>13563465.246355325</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="8">
+        <v>-19380981932</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="2"/>
+        <v>19155.900105757351</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="1">
         <v>45627</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="3">
         <v>6189529439.2326403</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="3">
         <v>12655121080</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="8">
         <v>1032.5</v>
       </c>
       <c r="E61">
@@ -4776,18 +5593,25 @@
         <f t="shared" si="1"/>
         <v>12256775.864406779</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="8">
+        <v>-19617869753</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="2"/>
+        <v>19000.358114285715</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>45658</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="3">
         <v>3356534397.2682099</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="3">
         <v>13532524154</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="8">
         <v>1053.5</v>
       </c>
       <c r="E62">
@@ -4798,18 +5622,25 @@
         <f t="shared" si="1"/>
         <v>12845300.573327005</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="G62" s="8">
+        <v>-21216656323</v>
+      </c>
+      <c r="H62" s="2">
+        <f t="shared" si="2"/>
+        <v>20139.208659705742</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>45689</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="3">
         <v>2937338690.3146801</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="3">
         <v>13222865246</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="8">
         <v>1064.375</v>
       </c>
       <c r="E63">
@@ -4820,18 +5651,25 @@
         <f t="shared" si="1"/>
         <v>12423126.478919555</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="8">
+        <v>-21334490010</v>
+      </c>
+      <c r="H63" s="2">
+        <f t="shared" si="2"/>
+        <v>20044.147983558425</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>45717</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="3">
         <v>2095645940.2700701</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="3">
         <v>12256776714</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="8">
         <v>1073.875</v>
       </c>
       <c r="E64">
@@ -4842,18 +5680,25 @@
         <f t="shared" si="1"/>
         <v>11413597.219415668</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="8">
+        <v>-21627605139</v>
+      </c>
+      <c r="H64" s="2">
+        <f t="shared" si="2"/>
+        <v>20139.778967756956</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="3">
         <v>18104955461.783604</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="3">
         <v>16055481356</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="8">
         <v>1172</v>
       </c>
       <c r="E65">
@@ -4864,18 +5709,25 @@
         <f t="shared" si="1"/>
         <v>13699216.174061434</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="8">
+        <v>-23601983312</v>
+      </c>
+      <c r="H65" s="2">
+        <f t="shared" si="2"/>
+        <v>20138.211017064845</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>45778</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="3">
         <v>3666728825.6510997</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="3">
         <v>14257299126</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="8">
         <v>1195.33</v>
       </c>
       <c r="E66">
@@ -4886,181 +5738,244 @@
         <f t="shared" si="1"/>
         <v>11927500.460960573</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="8">
+        <v>-24263323980</v>
+      </c>
+      <c r="H66" s="2">
+        <f t="shared" si="2"/>
+        <v>20298.431378782429</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>45809</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="3">
         <v>5588038328.8614292</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="3">
         <v>13737984886</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="8">
         <v>1194.0833</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E74" si="2">+B67/D67</f>
+        <f t="shared" ref="E67:E74" si="3">+B67/D67</f>
         <v>4679772.6162499962</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F74" si="3">+C67/D67</f>
+        <f t="shared" ref="F67:F74" si="4">+C67/D67</f>
         <v>11505047.33296245</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="8">
+        <v>-26767080944</v>
+      </c>
+      <c r="H67" s="2">
+        <f t="shared" ref="H67:H74" si="5">+-G67/(D67*1000)</f>
+        <v>22416.426847272716</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1">
         <v>45839</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="3">
         <v>3660591723.8559504</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="3">
         <v>16917145820</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="8">
         <v>1351.8333</v>
       </c>
       <c r="E68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2707872.1347195324</v>
       </c>
       <c r="F68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12514224.808635799</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68" s="8">
+        <v>-30118504542</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" si="5"/>
+        <v>22279.747467383735</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>45870</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="3">
         <v>2231611534.9542098</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="3">
         <v>16320310578</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="8">
         <v>1323.8333</v>
       </c>
       <c r="E69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1685719.4443999934</v>
       </c>
       <c r="F69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12328070.745765347</v>
       </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" s="8">
+        <v>-29738133453</v>
+      </c>
+      <c r="H69" s="2">
+        <f t="shared" si="5"/>
+        <v>22463.654187426771</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>45901</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="3">
         <v>3180587804.3659101</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="3">
         <v>17466352469</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="8">
         <v>1366.5833</v>
       </c>
       <c r="E70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2327401.3405299992</v>
       </c>
       <c r="F70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12781037.547436735</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="8">
+        <v>-30797118125</v>
+      </c>
+      <c r="H70" s="2">
+        <f t="shared" si="5"/>
+        <v>22535.851363762456</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>45931</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="3">
         <v>132674755.84999999</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="3">
         <v>20272509678</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="8">
         <v>1443</v>
       </c>
       <c r="E71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91943.697747747749</v>
       </c>
       <c r="F71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14048863.255717255</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71" s="8">
+        <v>-32468820360</v>
+      </c>
+      <c r="H71" s="2">
+        <f t="shared" si="5"/>
+        <v>22500.915010395009</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>45962</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="3">
         <v>308358184.73521996</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="3">
         <v>23190625070</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="8">
         <v>1450.75</v>
       </c>
       <c r="E72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>212550.87695000513</v>
       </c>
       <c r="F72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>15985266.289850077</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="8">
+        <v>-32797173611</v>
+      </c>
+      <c r="H72" s="2">
+        <f t="shared" si="5"/>
+        <v>22607.047121144235</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>45992</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="3">
         <v>2874845876.1723704</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="3">
         <v>21987630788</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="8">
         <v>1459.4167</v>
       </c>
       <c r="E73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1969859.51728</v>
       </c>
       <c r="F73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>15066040.280339399</v>
       </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="G73" s="8">
+        <v>-37044056094</v>
+      </c>
+      <c r="H73" s="2">
+        <f t="shared" si="5"/>
+        <v>25382.782103288253</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>46023</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="3">
         <v>761825004.98491001</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="3">
         <v>24998687967</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="8">
         <v>1447.6657</v>
       </c>
       <c r="E74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>526243.73498999805</v>
       </c>
       <c r="F74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17268273.99930799</v>
+      </c>
+      <c r="G74" s="8">
+        <v>-41152534525</v>
+      </c>
+      <c r="H74" s="2">
+        <f t="shared" si="5"/>
+        <v>28426.821554865881</v>
       </c>
     </row>
   </sheetData>
